--- a/output/rup/2026/Rekap RUP Tahun 2026 (2026-06-17) Legacy.xlsx
+++ b/output/rup/2026/Rekap RUP Tahun 2026 (2026-06-17) Legacy.xlsx
@@ -2241,19 +2241,19 @@
         <v>373421530</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>373421530</v>
+        <v>377271530</v>
       </c>
       <c r="E64" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>373421530</v>
+        <v>377271530</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>0</v>
+        <v>3850000</v>
       </c>
       <c r="H64" s="4" t="n">
-        <v>100</v>
+        <v>101.0310064339354</v>
       </c>
     </row>
     <row r="65">
@@ -2689,19 +2689,19 @@
         <v>11974816559</v>
       </c>
       <c r="D80" s="3" t="n">
-        <v>11799027759</v>
+        <v>11816260509</v>
       </c>
       <c r="E80" s="3" t="n">
         <v>175788800</v>
       </c>
       <c r="F80" s="3" t="n">
-        <v>11974816559</v>
+        <v>11992049309</v>
       </c>
       <c r="G80" s="3" t="n">
-        <v>0</v>
+        <v>17232750</v>
       </c>
       <c r="H80" s="4" t="n">
-        <v>100</v>
+        <v>100.143908258762</v>
       </c>
     </row>
     <row r="81">

--- a/output/rup/2026/Rekap RUP Tahun 2026 (2026-06-17) Legacy.xlsx
+++ b/output/rup/2026/Rekap RUP Tahun 2026 (2026-06-17) Legacy.xlsx
@@ -2689,19 +2689,19 @@
         <v>11974816559</v>
       </c>
       <c r="D80" s="3" t="n">
-        <v>11816260509</v>
+        <v>11799027759</v>
       </c>
       <c r="E80" s="3" t="n">
         <v>175788800</v>
       </c>
       <c r="F80" s="3" t="n">
-        <v>11992049309</v>
+        <v>11974816559</v>
       </c>
       <c r="G80" s="3" t="n">
-        <v>17232750</v>
+        <v>0</v>
       </c>
       <c r="H80" s="4" t="n">
-        <v>100.143908258762</v>
+        <v>100</v>
       </c>
     </row>
     <row r="81">

--- a/output/rup/2026/Rekap RUP Tahun 2026 (2026-06-17) Legacy.xlsx
+++ b/output/rup/2026/Rekap RUP Tahun 2026 (2026-06-17) Legacy.xlsx
@@ -2241,19 +2241,19 @@
         <v>373421530</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>377271530</v>
+        <v>373421530</v>
       </c>
       <c r="E64" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>377271530</v>
+        <v>373421530</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>3850000</v>
+        <v>0</v>
       </c>
       <c r="H64" s="4" t="n">
-        <v>101.0310064339354</v>
+        <v>100</v>
       </c>
     </row>
     <row r="65">

--- a/output/rup/2026/Rekap RUP Tahun 2026 (2026-06-17) Legacy.xlsx
+++ b/output/rup/2026/Rekap RUP Tahun 2026 (2026-06-17) Legacy.xlsx
@@ -1233,19 +1233,19 @@
         <v>1858317230</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>1858317230</v>
+        <v>1906317230</v>
       </c>
       <c r="E28" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>1858317230</v>
+        <v>1906317230</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>0</v>
+        <v>48000000</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>100</v>
+        <v>102.582982024011</v>
       </c>
     </row>
     <row r="29">
@@ -2689,19 +2689,19 @@
         <v>11974816559</v>
       </c>
       <c r="D80" s="3" t="n">
-        <v>11799027759</v>
+        <v>11816260509</v>
       </c>
       <c r="E80" s="3" t="n">
         <v>175788800</v>
       </c>
       <c r="F80" s="3" t="n">
-        <v>11974816559</v>
+        <v>11992049309</v>
       </c>
       <c r="G80" s="3" t="n">
-        <v>0</v>
+        <v>17232750</v>
       </c>
       <c r="H80" s="4" t="n">
-        <v>100</v>
+        <v>100.143908258762</v>
       </c>
     </row>
     <row r="81">

--- a/output/rup/2026/Rekap RUP Tahun 2026 (2026-06-17) Legacy.xlsx
+++ b/output/rup/2026/Rekap RUP Tahun 2026 (2026-06-17) Legacy.xlsx
@@ -1233,19 +1233,19 @@
         <v>1858317230</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>1906317230</v>
+        <v>1858317230</v>
       </c>
       <c r="E28" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>1906317230</v>
+        <v>1858317230</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>48000000</v>
+        <v>0</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>102.582982024011</v>
+        <v>100</v>
       </c>
     </row>
     <row r="29">
@@ -2689,19 +2689,19 @@
         <v>11974816559</v>
       </c>
       <c r="D80" s="3" t="n">
-        <v>11816260509</v>
+        <v>11799027759</v>
       </c>
       <c r="E80" s="3" t="n">
         <v>175788800</v>
       </c>
       <c r="F80" s="3" t="n">
-        <v>11992049309</v>
+        <v>11974816559</v>
       </c>
       <c r="G80" s="3" t="n">
-        <v>17232750</v>
+        <v>0</v>
       </c>
       <c r="H80" s="4" t="n">
-        <v>100.143908258762</v>
+        <v>100</v>
       </c>
     </row>
     <row r="81">
